--- a/Result/profitability/8908.xlsx
+++ b/Result/profitability/8908.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.48</v>
+        <v>0.49625</v>
       </c>
       <c r="N2" t="n">
-        <v>10.7125</v>
+        <v>10.64875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4375</v>
+        <v>0.42375</v>
       </c>
       <c r="N3" t="n">
-        <v>10.8325</v>
+        <v>10.6875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.12</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3675</v>
+        <v>0.37375</v>
       </c>
       <c r="N4" t="n">
-        <v>10.6475</v>
+        <v>10.79375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0.32125</v>
+        <v>0.31875</v>
       </c>
       <c r="N5" t="n">
-        <v>10.74875</v>
+        <v>10.7625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0.24875</v>
+        <v>0.26125</v>
       </c>
       <c r="N6" t="n">
-        <v>10.515</v>
+        <v>10.62</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.19375</v>
+        <v>0.18875</v>
       </c>
       <c r="N7" t="n">
-        <v>10.41625</v>
+        <v>10.22375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.11</v>
       </c>
       <c r="M8" t="n">
-        <v>0.13125</v>
+        <v>0.145</v>
       </c>
       <c r="N8" t="n">
-        <v>10.07125</v>
+        <v>10.15375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>0.10875</v>
       </c>
       <c r="N10" t="n">
-        <v>9.734999999999999</v>
+        <v>9.735000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8908</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2845</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2541</v>
+      </c>
+      <c r="E75" t="n">
+        <v>305</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="G75" t="n">
+        <v>238</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.36%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-12</v>
+      </c>
+      <c r="J75" t="n">
+        <v>226</v>
+      </c>
+      <c r="K75" t="n">
+        <v>178</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5425</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.75375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1099999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2391304347826084</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.6600000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06573705179282863</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.03389830508474578</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1099999999999994</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.01038715769593956</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
